--- a/params.xlsx
+++ b/params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YuKi_Project\R_Packages\RL\RLWMH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F54E810-0BBA-4A45-95E8-53C050B6AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7AD714-74CA-4CED-84AC-4346D53AFEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="2256" windowWidth="19320" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21156" yWindow="1740" windowWidth="19320" windowHeight="14352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="34">
   <si>
     <t>TD</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -87,10 +87,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>RLWM_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>alpha(RL)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -99,51 +95,63 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>RLWM_4(-weight)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>RLWM_4(-zeta)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>RLWM_4(-capacity)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>RLWM_5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>HWM_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>HWM_4(-weight)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>HWM_4(-zeta)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>HWM_4(-capacity)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>HWM_5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>sticky</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>RLWMH</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>lapse</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>H(decay)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RLWM</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSWM</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WMH</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>free/free</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RLWM(-weight)</t>
+  </si>
+  <si>
+    <t>RLWM(-zeta)</t>
+  </si>
+  <si>
+    <t>RLWM(-capacity)</t>
+  </si>
+  <si>
+    <t>HWM(-weight)</t>
+  </si>
+  <si>
+    <t>HWM(-zeta)</t>
+  </si>
+  <si>
+    <t>HWM(-capacity)</t>
+  </si>
+  <si>
+    <t>RLWM</t>
+  </si>
+  <si>
+    <t>HWM</t>
+  </si>
+  <si>
+    <t>special</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -231,7 +239,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -276,19 +284,6 @@
       <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
       <top/>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
@@ -322,7 +317,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -339,16 +334,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -641,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
@@ -652,10 +644,10 @@
     <row r="1" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
@@ -684,11 +676,11 @@
       <c r="L1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>29</v>
+      <c r="M1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
@@ -701,8 +693,8 @@
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
+      <c r="D2" s="4">
+        <v>25</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
@@ -728,10 +720,10 @@
       <c r="L2" s="1">
         <v>0.33</v>
       </c>
-      <c r="M2" s="11">
-        <v>0</v>
-      </c>
-      <c r="N2" s="11">
+      <c r="M2" s="10">
+        <v>0</v>
+      </c>
+      <c r="N2" s="10">
         <v>0.01</v>
       </c>
     </row>
@@ -745,8 +737,8 @@
       <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
+      <c r="D3" s="4">
+        <v>25</v>
       </c>
       <c r="E3" s="4">
         <v>1</v>
@@ -772,28 +764,28 @@
       <c r="L3" s="1">
         <v>0.33</v>
       </c>
-      <c r="M3" s="11">
-        <v>0</v>
-      </c>
-      <c r="N3" s="11">
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4">
+        <v>25</v>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -801,8 +793,8 @@
       <c r="G4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>9</v>
+      <c r="H4" s="4">
+        <v>0</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>10</v>
@@ -816,164 +808,164 @@
       <c r="L4" s="1">
         <v>0.33</v>
       </c>
-      <c r="M4" s="11">
-        <v>0</v>
-      </c>
-      <c r="N4" s="11">
+      <c r="M4" s="10">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="M5" s="11">
-        <v>0</v>
-      </c>
-      <c r="N5" s="11">
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>25</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-    </row>
-    <row r="7" spans="1:14" ht="16.2" thickTop="1">
-      <c r="A7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="M7" s="11">
-        <v>0</v>
-      </c>
-      <c r="N7" s="11">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="16.2" thickBot="1">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="M8" s="11">
-        <v>0</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0.01</v>
-      </c>
+    <row r="8" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -981,8 +973,8 @@
       <c r="C9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
+      <c r="D9" s="4">
+        <v>25</v>
       </c>
       <c r="E9" s="4">
         <v>1</v>
@@ -993,8 +985,8 @@
       <c r="G9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="4">
-        <v>0</v>
+      <c r="H9" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>9</v>
@@ -1008,16 +1000,16 @@
       <c r="L9" s="1">
         <v>0.33</v>
       </c>
-      <c r="M9" s="11">
-        <v>0</v>
-      </c>
-      <c r="N9" s="11">
+      <c r="M9" s="10">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>9</v>
@@ -1025,43 +1017,43 @@
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
+      <c r="D10" s="4">
+        <v>25</v>
       </c>
       <c r="E10" s="4">
         <v>1</v>
       </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="M10" s="11">
-        <v>0</v>
-      </c>
-      <c r="N10" s="11">
+      <c r="I10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A11" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>9</v>
@@ -1069,8 +1061,8 @@
       <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
+      <c r="D11" s="4">
+        <v>25</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
@@ -1081,8 +1073,8 @@
       <c r="G11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
+      <c r="H11" s="4">
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>9</v>
@@ -1096,76 +1088,76 @@
       <c r="L11" s="1">
         <v>0.33</v>
       </c>
-      <c r="M11" s="11">
-        <v>0</v>
-      </c>
-      <c r="N11" s="11">
+      <c r="M11" s="10">
+        <v>0</v>
+      </c>
+      <c r="N11" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13" spans="1:14" ht="16.2" thickTop="1">
-      <c r="A13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="L13" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="M13" s="11">
-        <v>0</v>
-      </c>
-      <c r="N13" s="11">
+      <c r="A12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>25</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="16.2" thickBot="1">
+    <row r="13" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+    </row>
+    <row r="14" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A14" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>9</v>
@@ -1173,43 +1165,43 @@
       <c r="C14" s="4">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
+      <c r="D14" s="4">
+        <v>25</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
       </c>
-      <c r="F14" s="6">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>10</v>
+      <c r="I14" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="L14" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="M14" s="11">
-        <v>0</v>
-      </c>
-      <c r="N14" s="11">
+      <c r="K14" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M14" s="10">
+        <v>0</v>
+      </c>
+      <c r="N14" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>9</v>
@@ -1217,43 +1209,43 @@
       <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>9</v>
+      <c r="D15" s="4">
+        <v>25</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
       </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>9</v>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K15" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="M15" s="11">
-        <v>0</v>
-      </c>
-      <c r="N15" s="11">
+      <c r="K15" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="M15" s="10">
+        <v>0</v>
+      </c>
+      <c r="N15" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A16" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
@@ -1261,8 +1253,8 @@
       <c r="C16" s="4">
         <v>1</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>9</v>
+      <c r="D16" s="4">
+        <v>25</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1273,14 +1265,14 @@
       <c r="G16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>9</v>
+      <c r="H16" s="4">
+        <v>0</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>10</v>
+      <c r="J16" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="K16" s="1">
         <v>0.33</v>
@@ -1288,16 +1280,16 @@
       <c r="L16" s="1">
         <v>0.33</v>
       </c>
-      <c r="M16" s="11">
-        <v>0</v>
-      </c>
-      <c r="N16" s="11">
+      <c r="M16" s="10">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>9</v>
@@ -1305,8 +1297,8 @@
       <c r="C17" s="4">
         <v>1</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>9</v>
+      <c r="D17" s="4">
+        <v>25</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1323,8 +1315,8 @@
       <c r="I17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>9</v>
+      <c r="J17" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="K17" s="1">
         <v>0.33</v>
@@ -1332,32 +1324,32 @@
       <c r="L17" s="1">
         <v>0.33</v>
       </c>
-      <c r="M17" s="11">
-        <v>0</v>
-      </c>
-      <c r="N17" s="11">
+      <c r="M17" s="10">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
     </row>
     <row r="19" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
       <c r="A19" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>9</v>
@@ -1365,8 +1357,8 @@
       <c r="C19" s="4">
         <v>1</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>9</v>
+      <c r="D19" s="4">
+        <v>25</v>
       </c>
       <c r="E19" s="4">
         <v>1</v>
@@ -1399,7 +1391,95 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="14.4" thickTop="1"/>
+    <row r="20" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4">
+        <v>25</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4">
+        <v>25</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="14.4" thickTop="1"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
